--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -806,16 +806,34 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>1.8</v>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -909,16 +927,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>0.493</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -978,16 +1014,34 @@
           <t>import_cover_months</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>4.954</v>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>months</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1064,16 +1118,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>78.372</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CBAR</t>
+          <t>Central Bank of Azerbaijan (refinancing rate)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -685,15 +685,29 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>State Statistical Committee</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -712,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jan-Aug-26</t>
+          <t>Jan-Aug 2026 y/y</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -725,11 +739,7 @@
           <t>Sep-26</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>y/y, non-oil +2.1%, oil/gas -0.8%</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -774,12 +784,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>01-Jun-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total government debt 24.1bn AZN / $14.18bn</t>
+          <t>total government debt, 24.1bn AZN ($14.18bn)</t>
         </is>
       </c>
     </row>
@@ -902,12 +912,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H1-26</t>
+          <t>H1 2026 (annualised GDP basis, approx.)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CBAR</t>
+          <t>Central Bank of Azerbaijan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -915,11 +925,7 @@
           <t>15-Sep-26</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>H1 surplus $4.74bn, ~10.5% of annualised GDP</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -972,22 +978,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>end-Sep-26</t>
+          <t>23-Sep-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CBAR</t>
+          <t>Central Bank of Azerbaijan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>23-Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBAR official reserves; SOFAZ assets $72.60bn additional (30-Jun-26)</t>
+          <t>CBAR official gross foreign exchange reserves (excludes SOFAZ assets of $72.60bn at 30-Jun-26; combined strategic FX assets $87.96bn)</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1092,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>01-Jun-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>external PUBLIC debt only (~$6.4bn)</t>
+          <t>direct external public (government) debt, ~$6.4bn; total economy external debt not sourced</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1174,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luxembourg Stock Exchange</t>
+          <t>Luxembourg Stock Exchange (USD 5.125% 2029 $310.7m + USD 3.500% 2032 $1,076.0m)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1176,11 +1182,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>$310.7m 2029 + $1,076.0m 2032</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1295,7 +1297,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>late 2025 (unsolicited)</t>
+          <t>22-May-26</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1319,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>18-Jun-26</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1331,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (Article IV)</t>
+          <t>None (Article IV surveillance only)</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1358,10 +1360,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1374,7 +1381,8 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1383,7 +1391,8 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1392,7 +1401,8 @@
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1400,10 +1410,11 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n">
         <v>10.5</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1412,7 +1423,8 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1421,7 +1433,8 @@
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1430,7 +1443,8 @@
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1439,7 +1453,8 @@
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1447,8 +1462,15 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" s="2" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Central Bank of Azerbaijan (CBAR gross FX reserves, end-2025), 23-Sep-26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1457,7 +1479,8 @@
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1466,7 +1489,8 @@
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/azerbaijan.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/azerbaijan.json</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan (refinancing rate)</t>
+          <t>Central Bank of Azerbaijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total government debt, 24.1bn AZN ($14.18bn)</t>
+          <t>Total government debt, 24.1bn AZN ($14.18bn)</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H1 2026 (annualised GDP basis, approx.)</t>
+          <t>H1-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan</t>
+          <t>Central Bank of Azerbaijan (approx., vs annualized GDP)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBAR official gross foreign exchange reserves (excludes SOFAZ assets of $72.60bn at 30-Jun-26; combined strategic FX assets $87.96bn)</t>
+          <t>CBAR gross foreign exchange reserves (excludes SOFAZ assets of $72.60bn at 30-Jun-26)</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>direct external public (government) debt, ~$6.4bn; total economy external debt not sourced</t>
+          <t>Direct external public (government) debt only, ~$6.4bn; not total external debt</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BB+</t>
+          <t>BB+ (unsolicited)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1468,7 +1468,7 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan (CBAR gross FX reserves, end-2025), 23-Sep-26</t>
+          <t>Central Bank of Azerbaijan, end-2025 CBAR gross FX reserves, 23-Sep-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan</t>
+          <t>Central Bank of Azerbaijan (refinancing rate)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total government debt, 24.1bn AZN ($14.18bn)</t>
+          <t>Total central government debt, 24.1bn AZN ($14.18bn)</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H1-26</t>
+          <t>H1 2026 (annualized GDP)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan (approx., vs annualized GDP)</t>
+          <t>Central Bank of Azerbaijan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4.954</v>
+        <v>50</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1030,24 +1030,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>mid-2026 (strategic FX assets $87.96bn incl. SOFAZ; stated as more than 50 months of merchandise import cover)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>SOFAZ / CBAR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1097,7 +1093,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Direct external public (government) debt only, ~$6.4bn; not total external debt</t>
+          <t>Direct external government debt (~$6.4bn); not total external debt</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1165,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>08-Oct-26 (USD 5.125% 2029 $310.7m + USD 3.500% 2032 $1,076.0m)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luxembourg Stock Exchange (USD 5.125% 2029 $310.7m + USD 3.500% 2032 $1,076.0m)</t>
+          <t>Luxembourg Stock Exchange</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1287,7 +1283,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BB+ (unsolicited)</t>
+          <t>BB+</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1465,10 +1461,12 @@
       <c r="B10" s="2" t="n">
         <v>11.51</v>
       </c>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="n">
+        <v>15.36</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan, end-2025 CBAR gross FX reserves, 23-Sep-26</t>
+          <t>Central Bank of Azerbaijan, 23-Sep-26 (2025 = end-2025 CBAR gross FX reserves; 2026E entry is the 23-Sep-26 spot level, not a year-end estimate)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total central government debt, 24.1bn AZN ($14.18bn)</t>
+          <t>total government debt, AZN 24.1bn ($14.18bn), domestic and external</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H1 2026 (annualized GDP)</t>
+          <t>H1-26 (approx., on annualised GDP)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBAR gross foreign exchange reserves (excludes SOFAZ assets of $72.60bn at 30-Jun-26)</t>
+          <t>CBAR official gross foreign exchange reserves, excl. SOFAZ assets ($72.60bn at 30-Jun-26; combined strategic FX assets $87.96bn)</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Direct external government debt (~$6.4bn); not total external debt</t>
+          <t>direct external public (government) debt, ~$6.4bn; excludes private and quasi-sovereign external debt</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08-Oct-26 (USD 5.125% 2029 $310.7m + USD 3.500% 2032 $1,076.0m)</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luxembourg Stock Exchange</t>
+          <t>Luxembourg Stock Exchange (USD 5.125% 2029 $310.7m + USD 3.500% 2032 $1,076.0m)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan, 23-Sep-26 (2025 = end-2025 CBAR gross FX reserves; 2026E entry is the 23-Sep-26 spot level, not a year-end estimate)</t>
+          <t>Central Bank of Azerbaijan, end-2025 CBAR gross FX reserves (derived from YTD change cited 23-Sep-26)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total government debt, AZN 24.1bn ($14.18bn), domestic and external</t>
+          <t>Total government debt, 24.1bn AZN ($14.18bn)</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H1-26 (approx., on annualised GDP)</t>
+          <t>H1 2026 (annualised GDP basis)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBAR official gross foreign exchange reserves, excl. SOFAZ assets ($72.60bn at 30-Jun-26; combined strategic FX assets $87.96bn)</t>
+          <t>CBAR gross foreign exchange reserves, excluding SOFAZ assets ($72.60bn at 30-Jun-26)</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>direct external public (government) debt, ~$6.4bn; excludes private and quasi-sovereign external debt</t>
+          <t>Direct external public (government) debt only, ~$6.4bn; not total external debt</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (Article IV surveillance only)</t>
+          <t>None active (Article IV surveillance only)</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan, end-2025 CBAR gross FX reserves (derived from YTD change cited 23-Sep-26)</t>
+          <t>Central Bank of Azerbaijan, end-2025 CBAR gross FX reserves as cited in run of 08-Oct-26 (reference 23-Sep-26 release)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan (refinancing rate)</t>
+          <t>Central Bank of Azerbaijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jan-Aug 2026 y/y</t>
+          <t>Jan-Aug 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total government debt, 24.1bn AZN ($14.18bn)</t>
+          <t>total government debt, AZN 24.1bn ($14.18bn)</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H1 2026 (annualised GDP basis)</t>
+          <t>H1-26 (approx., vs annualised GDP)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBAR gross foreign exchange reserves, excluding SOFAZ assets ($72.60bn at 30-Jun-26)</t>
+          <t>CBAR gross foreign exchange reserves (excludes SOFAZ assets of $72.60bn at 30-Jun-26)</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Direct external public (government) debt only, ~$6.4bn; not total external debt</t>
+          <t>government external debt (~$6.4bn); total external debt not sourced</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Luxembourg Stock Exchange (USD 5.125% 2029 $310.7m + USD 3.500% 2032 $1,076.0m)</t>
+          <t>Luxembourg Stock Exchange</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None active (Article IV surveillance only)</t>
+          <t>None (Article IV surveillance only)</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan, end-2025 CBAR gross FX reserves as cited in run of 08-Oct-26 (reference 23-Sep-26 release)</t>
+          <t>Central Bank of Azerbaijan, end-2025 value cited 23-Sep-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan</t>
+          <t>Central Bank of Azerbaijan, monetary policy decision (refinancing rate)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jan-Aug 2026</t>
+          <t>Jan-Aug 2026 y/y</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>total government debt, AZN 24.1bn ($14.18bn)</t>
+          <t>Total government debt, 24.1bn AZN ($14.18bn), external and domestic</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H1-26 (approx., vs annualised GDP)</t>
+          <t>H1 2026 (approx., vs annualised GDP)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBAR gross foreign exchange reserves (excludes SOFAZ assets of $72.60bn at 30-Jun-26)</t>
+          <t>CBAR gross foreign exchange reserves; excludes SOFAZ assets of $72.60bn (30-Jun-26); combined strategic FX assets $87.96bn</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>mid-2026 (strategic FX assets $87.96bn incl. SOFAZ; stated as more than 50 months of merchandise import cover)</t>
+          <t>mid-2026; floor ('more than 50 months'), merchandise imports, on strategic FX assets (SOFAZ + CBAR), not CBAR reserves alone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>government external debt (~$6.4bn); total external debt not sourced</t>
+          <t>Direct external government debt (~$6.4bn); excludes private-sector and quasi-sovereign external debt</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>08-Oct-26; USD 5.125% 2029 $310.7m + USD 3.500% 2032 $1,076.0m</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Central Bank of Azerbaijan, end-2025 value cited 23-Sep-26</t>
+          <t>Central Bank of Azerbaijan, CBAR gross FX reserves at end-2025, cited in report of 23-Sep-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/azerbaijan.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/azerbaijan.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/azerbaijan.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/azerbaijan.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Azerbaijan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/azerbaijan.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/azerbaijan.json</t>
         </is>
       </c>
     </row>
